--- a/data/trending_integrated_20260907_10.xlsx
+++ b/data/trending_integrated_20260907_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:Z17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53600</v>
+        <v>52800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+22.23%</t>
+          <t>+20.41%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.47</v>
       </c>
       <c r="E2" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="F2" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G2" t="n">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="H2" t="n">
         <v>14.18</v>
@@ -610,7 +610,7 @@
         <v>13.71</v>
       </c>
       <c r="O2" t="n">
-        <v>85083940325</v>
+        <v>91378657225</v>
       </c>
       <c r="P2" t="n">
         <v>108900</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>수익 전환 및 공매도 감소세 확인. 전고점 돌파 가능성 및 7만원 이상 목표 주가 전망.</t>
+          <t>상승 추세와 공매도 감소에 따른 강한 상승 기대감 및 수익 실현 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['수익 전환', '공매도', '전고점']</t>
+          <t>['상승추세', '공매도', '수익실현']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3765</v>
+        <v>3695</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+15.31%</t>
+          <t>+13.17%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.52</v>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H3" t="n">
         <v>1.25</v>
@@ -702,7 +702,7 @@
         <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>131866463949</v>
+        <v>138654130162</v>
       </c>
       <c r="P3" t="n">
         <v>3900</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>탈모약 관련 기대감 및 거래량 증가. 5천원 목표 주가 제시 및 3연상 가능성 언급.</t>
+          <t>탈모약 관련 이슈와 함께 단기 급등 및 3연상 기대감 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['탈모약', '거래량', '3연상']</t>
+          <t>['탈모약', '급등', '3연상']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8790</v>
+        <v>220000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+10.57%</t>
+          <t>+9.18%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.72</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>268</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>153</v>
       </c>
       <c r="G4" t="n">
-        <v>54</v>
+        <v>782</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6</v>
+        <v>29.46</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7950</v>
+        <v>201500</v>
       </c>
       <c r="K4" t="n">
-        <v>8200</v>
+        <v>212500</v>
       </c>
       <c r="L4" t="n">
-        <v>9210</v>
+        <v>225500</v>
       </c>
       <c r="M4" t="n">
-        <v>7980</v>
+        <v>212500</v>
       </c>
       <c r="N4" t="n">
-        <v>1.32</v>
+        <v>29.51</v>
       </c>
       <c r="O4" t="n">
-        <v>71826623070</v>
+        <v>226568504000</v>
       </c>
       <c r="P4" t="n">
-        <v>15960</v>
+        <v>438000</v>
       </c>
       <c r="Q4" t="n">
-        <v>3500</v>
+        <v>74700</v>
       </c>
       <c r="R4" t="n">
-        <v>208000</v>
+        <v>317000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>102000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미프진 관련 이슈 공식화 및 외국인/기관 매수세 유입 기대. 다만, 상승 추세는 제한적.</t>
+          <t>로봇 사업 및 액추에이터 기술 관련 호재와 프로그램 매수세 유입에 따른 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['미프진', '매수세', '상승']</t>
+          <t>['로봇사업', '액추에이터', '프로그램매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>066570</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>219000</v>
+        <v>8680</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+8.68%</t>
+          <t>+9.18%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.05</v>
+        <v>-0.72</v>
       </c>
       <c r="E5" t="n">
-        <v>257</v>
+        <v>48</v>
       </c>
       <c r="F5" t="n">
-        <v>148</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>745</v>
+        <v>60</v>
       </c>
       <c r="H5" t="n">
-        <v>29.46</v>
+        <v>0.6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>201500</v>
+        <v>7950</v>
       </c>
       <c r="K5" t="n">
-        <v>212500</v>
+        <v>8200</v>
       </c>
       <c r="L5" t="n">
-        <v>225500</v>
+        <v>9210</v>
       </c>
       <c r="M5" t="n">
-        <v>212500</v>
+        <v>7980</v>
       </c>
       <c r="N5" t="n">
-        <v>29.51</v>
+        <v>1.32</v>
       </c>
       <c r="O5" t="n">
-        <v>218009800000</v>
+        <v>76245412660</v>
       </c>
       <c r="P5" t="n">
-        <v>438000</v>
+        <v>15960</v>
       </c>
       <c r="Q5" t="n">
-        <v>74700</v>
+        <v>3500</v>
       </c>
       <c r="R5" t="n">
-        <v>317000</v>
+        <v>208000</v>
       </c>
       <c r="S5" t="n">
-        <v>102000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>로봇 액츄에이터 부품 기술력 기반 급등. 피지컬 AI 관련 투자 및 빅테크 협력 기대감 고조.</t>
+          <t>미프진 관련 이슈와 함께 주가 상승 기대감 및 단기 매매 관점의 글 다수.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['로봇 액츄에이터', '피지컬 AI', '빅테크']</t>
+          <t>['미프진', '단기매매', '주가']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24900</v>
+        <v>25350</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+5.96%</t>
+          <t>+7.87%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>230</v>
+        <v>281</v>
       </c>
       <c r="F6" t="n">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="G6" t="n">
-        <v>304</v>
+        <v>341</v>
       </c>
       <c r="H6" t="n">
         <v>0.16</v>
@@ -969,7 +969,7 @@
         <v>23200</v>
       </c>
       <c r="L6" t="n">
-        <v>25600</v>
+        <v>26450</v>
       </c>
       <c r="M6" t="n">
         <v>22800</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>192688563325</v>
+        <v>280986319875</v>
       </c>
       <c r="P6" t="n">
         <v>28750</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>CART 혈압계 관련 뉴스 및 세계 최초/1위 기술력 보유. 다만, 적자 기업 및 고평가 논란 존재.</t>
+          <t>의료기기 및 혈압계 관련 뉴스 기반 상승 기대와 함께 매집 및 단기 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['CART 혈압계', '의료기기', '적자']</t>
+          <t>['의료기기', '혈압계', '매집']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6180</v>
+        <v>6230</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+5.64%</t>
+          <t>+6.50%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.7</v>
       </c>
       <c r="E7" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="H7" t="n">
         <v>1.61</v>
@@ -1070,7 +1070,7 @@
         <v>2.31</v>
       </c>
       <c r="O7" t="n">
-        <v>9846018855</v>
+        <v>10298601465</v>
       </c>
       <c r="P7" t="n">
         <v>21500</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1733000</v>
+        <v>1741000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.22%</t>
+          <t>+5.71%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="F8" t="n">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G8" t="n">
-        <v>1947</v>
+        <v>1889</v>
       </c>
       <c r="H8" t="n">
         <v>50.5</v>
@@ -1162,7 +1162,7 @@
         <v>50.45</v>
       </c>
       <c r="O8" t="n">
-        <v>1562468445500</v>
+        <v>1653003990000</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>자사주 매입 예정 및 외인 매수세 유입에 따른 200만원 돌파 기대감.</t>
+          <t>자사주 매입과 200만원 돌파에 대한 기대감 표출. 상승 추세 진입 및 외인 매집 정황.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주매입', '외인매집', '주가전망']</t>
+          <t>['자사주매입', '상승추세', '외인매집']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83300</v>
+        <v>83400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.18%</t>
+          <t>+5.30%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G9" t="n">
-        <v>250</v>
+        <v>302</v>
       </c>
       <c r="H9" t="n">
         <v>23.53</v>
@@ -1254,7 +1254,7 @@
         <v>23.61</v>
       </c>
       <c r="O9" t="n">
-        <v>107081084850</v>
+        <v>113283186850</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>하반기 수주 기대감 및 원자력주 전반의 상승세. 10만원 돌파 가능성 및 83000원대 매물 소화 중.</t>
+          <t>하반기 수주 및 대미 투자 관련 긍정적 전망과 함께 원자력주 전반의 상승세 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['수주', '원자력주', '매물 소화']</t>
+          <t>['하반기수주', '대미투자', '원자력']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,70 +1299,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13590</v>
+        <v>17590</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.46%</t>
+          <t>+4.39%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.09</v>
+        <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>193</v>
+        <v>122</v>
       </c>
       <c r="H10" t="n">
-        <v>1.82</v>
+        <v>10.4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13010</v>
+        <v>16850</v>
       </c>
       <c r="K10" t="n">
-        <v>13420</v>
+        <v>16870</v>
       </c>
       <c r="L10" t="n">
-        <v>14100</v>
+        <v>17770</v>
       </c>
       <c r="M10" t="n">
-        <v>13410</v>
+        <v>16590</v>
       </c>
       <c r="N10" t="n">
-        <v>1.91</v>
+        <v>10.36</v>
       </c>
       <c r="O10" t="n">
-        <v>51258681645</v>
+        <v>50735908700</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>1252</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>204000</v>
+        <v>82000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>광통신주 상승 추세 및 미국 시장 동반 상승 기대. 다만, 주가 변동성이 크고 14000원대 매물 부담 존재.</t>
+          <t>러우 전쟁 종전 분위기와 원전 관련 이슈로 인한 상승 기대 및 단기 수익 실현 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신주', '상승 추세', '변동성']</t>
+          <t>['러우전쟁', '원전', '수익실현']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>264250</v>
+        <v>13580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+3.42%</t>
+          <t>+4.38%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>781</v>
+        <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>456</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>2901</v>
+        <v>211</v>
       </c>
       <c r="H11" t="n">
-        <v>46.73</v>
+        <v>1.82</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>255500</v>
+        <v>13010</v>
       </c>
       <c r="K11" t="n">
-        <v>267000</v>
+        <v>13420</v>
       </c>
       <c r="L11" t="n">
-        <v>268000</v>
+        <v>14100</v>
       </c>
       <c r="M11" t="n">
-        <v>264000</v>
+        <v>13410</v>
       </c>
       <c r="N11" t="n">
-        <v>46.71</v>
+        <v>1.91</v>
       </c>
       <c r="O11" t="n">
-        <v>1088118218250</v>
+        <v>52941862185</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>69600</v>
+        <v>1252</v>
       </c>
       <c r="R11" t="n">
-        <v>1074000</v>
+        <v>204000</v>
       </c>
       <c r="S11" t="n">
-        <v>809000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>삼성전자, 30만원 터치 및 50~60만+a 목표주가 언급. 배당 기대와 함께 단기 매도 의견도 혼재.</t>
+          <t>광통신주 대장주로서의 기대감 및 공매도 현황 언급. 주가 변동성에 대한 의견 교환.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['목표주가', '배당', '매도']</t>
+          <t>['공매도', '대장주', '변동성']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23150</v>
+        <v>265000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+2.89%</t>
+          <t>+3.72%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.62</v>
+        <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>792</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>463</v>
       </c>
       <c r="G12" t="n">
-        <v>99</v>
+        <v>2674</v>
       </c>
       <c r="H12" t="n">
-        <v>5.6</v>
+        <v>46.73</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>22500</v>
+        <v>255500</v>
       </c>
       <c r="K12" t="n">
-        <v>23100</v>
+        <v>267000</v>
       </c>
       <c r="L12" t="n">
-        <v>24000</v>
+        <v>268000</v>
       </c>
       <c r="M12" t="n">
-        <v>21500</v>
+        <v>264000</v>
       </c>
       <c r="N12" t="n">
-        <v>4.98</v>
+        <v>46.71</v>
       </c>
       <c r="O12" t="n">
-        <v>102752774350</v>
+        <v>1139126873500</v>
       </c>
       <c r="P12" t="n">
-        <v>50600</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>9070</v>
+        <v>69600</v>
       </c>
       <c r="R12" t="n">
-        <v>-51000</v>
+        <v>1074000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>809000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>로봇 관련주로 인한 상승 기대감, 단기 급등 후 변동성 출현.</t>
+          <t>배당 및 반도체 이슈를 기반으로 한 상승 기대감과 목표 주가 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['로봇', '신사업', '변동성']</t>
+          <t>['배당', '반도체', '목표주가']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10440</v>
+        <v>23050</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.48%</t>
+          <t>+2.44%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.05</v>
+        <v>0.62</v>
       </c>
       <c r="E13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="H13" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>10390</v>
+        <v>22500</v>
       </c>
       <c r="K13" t="n">
-        <v>10050</v>
+        <v>23100</v>
       </c>
       <c r="L13" t="n">
-        <v>11000</v>
+        <v>24000</v>
       </c>
       <c r="M13" t="n">
-        <v>9770</v>
+        <v>21500</v>
       </c>
       <c r="N13" t="n">
-        <v>5.7</v>
+        <v>4.98</v>
       </c>
       <c r="O13" t="n">
-        <v>16099632815</v>
+        <v>108890589525</v>
       </c>
       <c r="P13" t="n">
-        <v>15640</v>
+        <v>50600</v>
       </c>
       <c r="Q13" t="n">
-        <v>5470</v>
+        <v>9070</v>
       </c>
       <c r="R13" t="n">
-        <v>-84000</v>
+        <v>-51000</v>
       </c>
       <c r="S13" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>호재 발생 및 공매도 세력과의 공방 속 200만원 목표 주가 기대.</t>
+          <t>로봇주 테마와 신사업 진출 기대감 속에서 단기 급등 및 거래량 주목.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['호재', '공매도', '주가목표']</t>
+          <t>['로봇주', '신사업', '거래량']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16100</v>
+        <v>16130</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F14" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G14" t="n">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>22033196395</v>
+        <v>23991815880</v>
       </c>
       <c r="P14" t="n">
         <v>19380</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>메가특구법 발의 및 호남 반도체 산단 관련 긍정적 뉴스. 다만, 투자 주체별 매매 동향은 혼조세.</t>
+          <t>신규 사업 및 인프라 투자 관련 언급과 함께 개별 주포에 대한 기대감 혼재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['메가특구법', '반도체 산단', '투자 심리']</t>
+          <t>['신규사업', '인프라', '주포']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>아난티</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5440</v>
+        <v>10360</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-4.73%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.42</v>
+        <v>0.05</v>
       </c>
       <c r="E15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="H15" t="n">
-        <v>4.81</v>
+        <v>5.75</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>5710</v>
+        <v>10390</v>
       </c>
       <c r="K15" t="n">
-        <v>5640</v>
+        <v>10050</v>
       </c>
       <c r="L15" t="n">
-        <v>5650</v>
+        <v>11000</v>
       </c>
       <c r="M15" t="n">
-        <v>5270</v>
+        <v>9770</v>
       </c>
       <c r="N15" t="n">
-        <v>4.39</v>
+        <v>5.7</v>
       </c>
       <c r="O15" t="n">
-        <v>10881645515</v>
+        <v>16599223805</v>
       </c>
       <c r="P15" t="n">
-        <v>10480</v>
+        <v>15640</v>
       </c>
       <c r="Q15" t="n">
-        <v>3150</v>
+        <v>5470</v>
       </c>
       <c r="R15" t="n">
-        <v>-307000</v>
+        <v>-84000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>대북주 테마 부각 및 금강산 관광 기대. 다만, 외인/연기금 매수세에도 불구하고 주가 하락 및 도박주 리스크 존재.</t>
+          <t>주가 상승에 대한 기대감과 함께 공매도에 대한 부정적 의견. 호재 발생 가능성 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['대북주', '금강산 관광', '도박주']</t>
+          <t>['공매도', '호재', '주가상승']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>025980</t>
+          <t>064550</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>아난티</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5310</v>
+        <v>5450</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-7.49%</t>
+          <t>-4.55%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="E16" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G16" t="n">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>5740</v>
+        <v>5710</v>
       </c>
       <c r="K16" t="n">
-        <v>5250</v>
+        <v>5640</v>
       </c>
       <c r="L16" t="n">
-        <v>5420</v>
+        <v>5650</v>
       </c>
       <c r="M16" t="n">
-        <v>5000</v>
+        <v>5270</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="O16" t="n">
-        <v>2152749210</v>
+        <v>11409265005</v>
       </c>
       <c r="P16" t="n">
-        <v>9680</v>
+        <v>10480</v>
       </c>
       <c r="Q16" t="n">
-        <v>371</v>
+        <v>3150</v>
       </c>
       <c r="R16" t="n">
-        <v>-10000</v>
+        <v>-307000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 및 구주 매각 이슈로 인한 악재 발생, 하한가 기록.</t>
+          <t>하락세에 대한 우려와 함께 외인·연기금의 매수세, 북한 관련 이슈 언급. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,18 +1923,110 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>['외인매수', '대북주', '주가조작']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>025980</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>본느</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5250</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-8.54%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>75</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42</v>
+      </c>
+      <c r="G17" t="n">
+        <v>161</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>5740</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5250</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5420</v>
+      </c>
+      <c r="M17" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2290123640</v>
+      </c>
+      <c r="P17" t="n">
+        <v>9680</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>371</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>반기보고서 제출 지연 및 구주 매각 이슈로 인한 악재 발생, 하한가 기록.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
           <t>['반기보고서', '악재', '하한가']</t>
         </is>
       </c>
-      <c r="X16" t="n">
+      <c r="X17" t="n">
         <v>1</v>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>226340</t>
         </is>

--- a/data/trending_integrated_20260907_10.xlsx
+++ b/data/trending_integrated_20260907_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52800</v>
+        <v>52300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+20.41%</t>
+          <t>+19.27%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.47</v>
       </c>
       <c r="E2" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G2" t="n">
-        <v>390</v>
+        <v>419</v>
       </c>
       <c r="H2" t="n">
         <v>14.18</v>
@@ -610,7 +610,7 @@
         <v>13.71</v>
       </c>
       <c r="O2" t="n">
-        <v>91378657225</v>
+        <v>96427909375</v>
       </c>
       <c r="P2" t="n">
         <v>108900</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>상승 추세와 공매도 감소에 따른 강한 상승 기대감 및 수익 실현 언급.</t>
+          <t>공매도 감소 및 우상향 추세 언급, 전고점 돌파 및 6-7만원 구간 매물대 약화 전망. 큰 폭 상승 마감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['상승추세', '공매도', '수익실현']</t>
+          <t>['공매도', '우상향', '매물대']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3695</v>
+        <v>3655</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+13.17%</t>
+          <t>+11.94%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.52</v>
       </c>
       <c r="E3" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G3" t="n">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="H3" t="n">
         <v>1.25</v>
@@ -702,7 +702,7 @@
         <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>138654130162</v>
+        <v>143932071492</v>
       </c>
       <c r="P3" t="n">
         <v>3900</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>탈모약 관련 이슈와 함께 단기 급등 및 3연상 기대감 언급.</t>
+          <t>바이오니아, 삼익 등 타 종목 언급과 함께 긍정적 흐름 기대. '60% 상승' 등 구체적 전망 제시. 큰 폭 상승 마감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['탈모약', '급등', '3연상']</t>
+          <t>['바이오니아', '상승 전망']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="F4" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="G4" t="n">
-        <v>782</v>
+        <v>799</v>
       </c>
       <c r="H4" t="n">
         <v>29.46</v>
@@ -794,7 +794,7 @@
         <v>29.51</v>
       </c>
       <c r="O4" t="n">
-        <v>226568504000</v>
+        <v>235319289500</v>
       </c>
       <c r="P4" t="n">
         <v>438000</v>
@@ -839,83 +839,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8680</v>
+        <v>6370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+9.18%</t>
+          <t>+8.89%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.72</v>
+        <v>-0.7</v>
       </c>
       <c r="E5" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>227</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6</v>
+        <v>1.61</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7950</v>
+        <v>5850</v>
       </c>
       <c r="K5" t="n">
-        <v>8200</v>
+        <v>6000</v>
       </c>
       <c r="L5" t="n">
-        <v>9210</v>
+        <v>6490</v>
       </c>
       <c r="M5" t="n">
-        <v>7980</v>
+        <v>5940</v>
       </c>
       <c r="N5" t="n">
-        <v>1.32</v>
+        <v>2.31</v>
       </c>
       <c r="O5" t="n">
-        <v>76245412660</v>
+        <v>10650637125</v>
       </c>
       <c r="P5" t="n">
-        <v>15960</v>
+        <v>21500</v>
       </c>
       <c r="Q5" t="n">
-        <v>3500</v>
+        <v>2300</v>
       </c>
       <c r="R5" t="n">
-        <v>208000</v>
+        <v>-35000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미프진 관련 이슈와 함께 주가 상승 기대감 및 단기 매매 관점의 글 다수.</t>
+          <t>세계폐암학회 관련 뉴스와 신약 개발 가능성에 대한 기대감이 높음. 보유 및 저점 추매 권유가 있으며, 공매도에 대한 언급도 존재. 주가 상승에 대한 강한 의지 표현.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['미프진', '단기매매', '주가']</t>
+          <t>['신약 개발', '세계폐암학회', '공매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25350</v>
+        <v>8600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+7.87%</t>
+          <t>+8.18%</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="E6" t="n">
+        <v>52</v>
+      </c>
+      <c r="F6" t="n">
+        <v>36</v>
+      </c>
+      <c r="G6" t="n">
+        <v>85</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>7950</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8200</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9210</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7980</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="O6" t="n">
+        <v>78960682395</v>
+      </c>
+      <c r="P6" t="n">
+        <v>15960</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3500</v>
+      </c>
+      <c r="R6" t="n">
+        <v>208000</v>
+      </c>
+      <c r="S6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="n">
-        <v>281</v>
-      </c>
-      <c r="F6" t="n">
-        <v>138</v>
-      </c>
-      <c r="G6" t="n">
-        <v>341</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>23500</v>
-      </c>
-      <c r="K6" t="n">
-        <v>23200</v>
-      </c>
-      <c r="L6" t="n">
-        <v>26450</v>
-      </c>
-      <c r="M6" t="n">
-        <v>22800</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>280986319875</v>
-      </c>
-      <c r="P6" t="n">
-        <v>28750</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>8200</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-1000</v>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>의료기기 및 혈압계 관련 뉴스 기반 상승 기대와 함께 매집 및 단기 급등 가능성 언급.</t>
+          <t>미프진 관련 언급 다수, 시장 기대감은 있으나 뚜렷한 근거 제시 부족. 등락률 소폭 상승.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['의료기기', '혈압계', '매집']</t>
+          <t>['미프진', '기대감']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6230</v>
+        <v>25000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+6.50%</t>
+          <t>+6.38%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>58</v>
+        <v>307</v>
       </c>
       <c r="F7" t="n">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="G7" t="n">
-        <v>205</v>
+        <v>359</v>
       </c>
       <c r="H7" t="n">
-        <v>1.61</v>
+        <v>0.16</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>5850</v>
+        <v>23500</v>
       </c>
       <c r="K7" t="n">
-        <v>6000</v>
+        <v>23200</v>
       </c>
       <c r="L7" t="n">
-        <v>6490</v>
+        <v>26450</v>
       </c>
       <c r="M7" t="n">
-        <v>5940</v>
+        <v>22800</v>
       </c>
       <c r="N7" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>10298601465</v>
+        <v>321941425550</v>
       </c>
       <c r="P7" t="n">
-        <v>21500</v>
+        <v>28750</v>
       </c>
       <c r="Q7" t="n">
-        <v>2300</v>
+        <v>8200</v>
       </c>
       <c r="R7" t="n">
-        <v>-35000</v>
+        <v>-2000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>신약 개발 가능성 및 현대바이오와의 연관성 언급. 다만, 허황된 꿈이라는 부정적 시각 및 고점 매도 주의 필요.</t>
+          <t>CART 혈압계 관련 뉴스 언급, 서울대 등 유수 기관 협력 기반. 단기 급등 후 조정 및 향후 급등 가능성 언급. 소폭 상승 마감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['신약 개발', '현대바이오', '고점 매도']</t>
+          <t>['CART', '혈압계', '협력']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1741000</v>
+        <v>1744000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.71%</t>
+          <t>+5.89%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>797</v>
       </c>
       <c r="F8" t="n">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="G8" t="n">
-        <v>1889</v>
+        <v>1914</v>
       </c>
       <c r="H8" t="n">
         <v>50.5</v>
@@ -1162,7 +1162,7 @@
         <v>50.45</v>
       </c>
       <c r="O8" t="n">
-        <v>1653003990000</v>
+        <v>1784139813000</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>자사주 매입과 200만원 돌파에 대한 기대감 표출. 상승 추세 진입 및 외인 매집 정황.</t>
+          <t>자사주 매입 및 외국인/기관 순매수세 유입에 따른 주가 상승 기대감 높음. 200만원 돌파 및 고공 행진 전망. 숏커버링 가능성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주매입', '상승추세', '외인매집']</t>
+          <t>['자사주매입', '외국인순매수', '숏커버링']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83400</v>
+        <v>82900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.30%</t>
+          <t>+4.67%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F9" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G9" t="n">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="H9" t="n">
         <v>23.53</v>
@@ -1254,7 +1254,7 @@
         <v>23.61</v>
       </c>
       <c r="O9" t="n">
-        <v>113283186850</v>
+        <v>119518966050</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>하반기 수주 및 대미 투자 관련 긍정적 전망과 함께 원자력주 전반의 상승세 언급.</t>
+          <t>하반기 본격 수주 및 대형 원전, 가스복합화력발전 언급. 기술력 입증 기반 상승 추세 전망. 큰 폭 상승 마감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['하반기수주', '대미투자', '원자력']</t>
+          <t>['하반기 수주', '대형 원전', '기술력']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,70 +1299,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17590</v>
+        <v>13530</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.39%</t>
+          <t>+4.00%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="E10" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>122</v>
+        <v>214</v>
       </c>
       <c r="H10" t="n">
-        <v>10.4</v>
+        <v>1.82</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>16850</v>
+        <v>13010</v>
       </c>
       <c r="K10" t="n">
-        <v>16870</v>
+        <v>13420</v>
       </c>
       <c r="L10" t="n">
-        <v>17770</v>
+        <v>14100</v>
       </c>
       <c r="M10" t="n">
-        <v>16590</v>
+        <v>13410</v>
       </c>
       <c r="N10" t="n">
-        <v>10.36</v>
+        <v>1.91</v>
       </c>
       <c r="O10" t="n">
-        <v>50735908700</v>
+        <v>54829891005</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>1252</v>
       </c>
       <c r="R10" t="n">
-        <v>82000</v>
+        <v>204000</v>
       </c>
       <c r="S10" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>러우 전쟁 종전 분위기와 원전 관련 이슈로 인한 상승 기대 및 단기 수익 실현 언급.</t>
+          <t>회사의 가치를 긍정적으로 평가하며, 당일 광통신주 대장으로서의 역할 기대. 공매도 물량 언급과 함께 주가 변동성에 대한 언급 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['러우전쟁', '원전', '수익실현']</t>
+          <t>['광통신주', '공매도', '주가 변동성']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13580</v>
+        <v>264750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+4.38%</t>
+          <t>+3.62%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.09</v>
+        <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>49</v>
+        <v>795</v>
       </c>
       <c r="F11" t="n">
-        <v>38</v>
+        <v>460</v>
       </c>
       <c r="G11" t="n">
-        <v>211</v>
+        <v>2492</v>
       </c>
       <c r="H11" t="n">
-        <v>1.82</v>
+        <v>46.73</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13010</v>
+        <v>255500</v>
       </c>
       <c r="K11" t="n">
-        <v>13420</v>
+        <v>267000</v>
       </c>
       <c r="L11" t="n">
-        <v>14100</v>
+        <v>268000</v>
       </c>
       <c r="M11" t="n">
-        <v>13410</v>
+        <v>264000</v>
       </c>
       <c r="N11" t="n">
-        <v>1.91</v>
+        <v>46.71</v>
       </c>
       <c r="O11" t="n">
-        <v>52941862185</v>
+        <v>1203393250000</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>1252</v>
+        <v>69600</v>
       </c>
       <c r="R11" t="n">
-        <v>204000</v>
+        <v>1074000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>809000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>광통신주 대장주로서의 기대감 및 공매도 현황 언급. 주가 변동성에 대한 의견 교환.</t>
+          <t>배당 및 목표 주가 언급, 반도체 관련 뉴스 인용. 긍정적 전망과 더불어 소폭 상승 마감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['공매도', '대장주', '변동성']</t>
+          <t>['배당', '목표 주가', '반도체']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>265000</v>
+        <v>17400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.72%</t>
+          <t>+3.26%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>792</v>
+        <v>43</v>
       </c>
       <c r="F12" t="n">
-        <v>463</v>
+        <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>2674</v>
+        <v>128</v>
       </c>
       <c r="H12" t="n">
-        <v>46.73</v>
+        <v>10.4</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>255500</v>
+        <v>16850</v>
       </c>
       <c r="K12" t="n">
-        <v>267000</v>
+        <v>16870</v>
       </c>
       <c r="L12" t="n">
-        <v>268000</v>
+        <v>17770</v>
       </c>
       <c r="M12" t="n">
-        <v>264000</v>
+        <v>16590</v>
       </c>
       <c r="N12" t="n">
-        <v>46.71</v>
+        <v>10.36</v>
       </c>
       <c r="O12" t="n">
-        <v>1139126873500</v>
+        <v>54569644560</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>69600</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>1074000</v>
+        <v>82000</v>
       </c>
       <c r="S12" t="n">
-        <v>809000</v>
+        <v>-8000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>배당 및 반도체 이슈를 기반으로 한 상승 기대감과 목표 주가 언급.</t>
+          <t>러우 전쟁 종전 분위기 및 중동 관련 언급, 주가 상승 기대감 표출. 소폭 상승 마감.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['배당', '반도체', '목표주가']</t>
+          <t>['러우 전쟁', '중동']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23050</v>
+        <v>6850</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+2.44%</t>
+          <t>+2.09%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="E13" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F13" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="H13" t="n">
-        <v>5.6</v>
+        <v>16.4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22500</v>
+        <v>6710</v>
       </c>
       <c r="K13" t="n">
-        <v>23100</v>
+        <v>6680</v>
       </c>
       <c r="L13" t="n">
-        <v>24000</v>
+        <v>7040</v>
       </c>
       <c r="M13" t="n">
-        <v>21500</v>
+        <v>6600</v>
       </c>
       <c r="N13" t="n">
-        <v>4.98</v>
+        <v>15.55</v>
       </c>
       <c r="O13" t="n">
-        <v>108890589525</v>
+        <v>7271284755</v>
       </c>
       <c r="P13" t="n">
-        <v>50600</v>
+        <v>13000</v>
       </c>
       <c r="Q13" t="n">
-        <v>9070</v>
+        <v>6030</v>
       </c>
       <c r="R13" t="n">
-        <v>-51000</v>
+        <v>2000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>로봇주 테마와 신사업 진출 기대감 속에서 단기 급등 및 거래량 주목.</t>
+          <t>반도체 및 로봇 관련 언급, IPO 예정 기업 존재. 주가 부양 기대와 함께 '폭락주', '개미 털기' 등 부정적 언급 혼재. 소폭 상승 마감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['로봇주', '신사업', '거래량']</t>
+          <t>['반도체', '로봇', 'IPO']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16130</v>
+        <v>22750</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G14" t="n">
-        <v>274</v>
+        <v>104</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>16090</v>
+        <v>22500</v>
       </c>
       <c r="K14" t="n">
-        <v>16150</v>
+        <v>23100</v>
       </c>
       <c r="L14" t="n">
-        <v>16480</v>
+        <v>24000</v>
       </c>
       <c r="M14" t="n">
-        <v>15830</v>
+        <v>21500</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="O14" t="n">
-        <v>23991815880</v>
+        <v>112588277225</v>
       </c>
       <c r="P14" t="n">
-        <v>19380</v>
+        <v>50600</v>
       </c>
       <c r="Q14" t="n">
-        <v>3200</v>
+        <v>9070</v>
       </c>
       <c r="R14" t="n">
-        <v>-3000</v>
+        <v>-51000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>신규 사업 및 인프라 투자 관련 언급과 함께 개별 주포에 대한 기대감 혼재.</t>
+          <t>국민성장펀드 관련 언급과 함께 거래량에 주목. 신사업 진출 및 로봇주 테마 상승 기대감 존재. 그러나 단기 급등락 및 투자주의 종목 지정 언급으로 변동성 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['신규사업', '인프라', '주포']</t>
+          <t>['국민성장펀드', '로봇주', '거래량']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10360</v>
+        <v>30250</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F15" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G15" t="n">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="H15" t="n">
-        <v>5.75</v>
+        <v>48.88</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>10390</v>
+        <v>30200</v>
       </c>
       <c r="K15" t="n">
-        <v>10050</v>
+        <v>30350</v>
       </c>
       <c r="L15" t="n">
-        <v>11000</v>
+        <v>30900</v>
       </c>
       <c r="M15" t="n">
-        <v>9770</v>
+        <v>29900</v>
       </c>
       <c r="N15" t="n">
-        <v>5.7</v>
+        <v>24.02</v>
       </c>
       <c r="O15" t="n">
-        <v>16599223805</v>
+        <v>46245487700</v>
       </c>
       <c r="P15" t="n">
-        <v>15640</v>
+        <v>31200</v>
       </c>
       <c r="Q15" t="n">
-        <v>5470</v>
+        <v>21000</v>
       </c>
       <c r="R15" t="n">
-        <v>-84000</v>
+        <v>139000</v>
       </c>
       <c r="S15" t="n">
-        <v>-2000</v>
+        <v>28000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 상승에 대한 기대감과 함께 공매도에 대한 부정적 의견. 호재 발생 가능성 언급.</t>
+          <t>정배열 우상향 추세 및 공매도 물량 언급, 3만원 구간 지지선 기대. 소폭 상승 마감.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공매도', '호재', '주가상승']</t>
+          <t>['정배열', '공매도', '지지선']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>아난티</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5450</v>
+        <v>16080</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.55%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F16" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G16" t="n">
-        <v>148</v>
+        <v>287</v>
       </c>
       <c r="H16" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>5710</v>
+        <v>16090</v>
       </c>
       <c r="K16" t="n">
-        <v>5640</v>
+        <v>16150</v>
       </c>
       <c r="L16" t="n">
-        <v>5650</v>
+        <v>16480</v>
       </c>
       <c r="M16" t="n">
-        <v>5270</v>
+        <v>15830</v>
       </c>
       <c r="N16" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>11409265005</v>
+        <v>24994319225</v>
       </c>
       <c r="P16" t="n">
-        <v>10480</v>
+        <v>19380</v>
       </c>
       <c r="Q16" t="n">
-        <v>3150</v>
+        <v>3200</v>
       </c>
       <c r="R16" t="n">
-        <v>-307000</v>
+        <v>-3000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>하락세에 대한 우려와 함께 외인·연기금의 매수세, 북한 관련 이슈 언급. 주가 조작 의혹 제기.</t>
+          <t>메가 특구법 발의 및 호남 반도체 산단 관련 언급, 주가 상승 기대감 있으나 '개잡주' 등 부정적 표현 혼재. 소폭 하락 마감.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['외인매수', '대북주', '주가조작']</t>
+          <t>['메가 특구법', '반도체 산단', '개잡주']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>025980</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5250</v>
+        <v>10340</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-8.54%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="F17" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G17" t="n">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,47 +1975,47 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>5740</v>
+        <v>10390</v>
       </c>
       <c r="K17" t="n">
-        <v>5250</v>
+        <v>10050</v>
       </c>
       <c r="L17" t="n">
-        <v>5420</v>
+        <v>11000</v>
       </c>
       <c r="M17" t="n">
-        <v>5000</v>
+        <v>9770</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O17" t="n">
-        <v>2290123640</v>
+        <v>16925165495</v>
       </c>
       <c r="P17" t="n">
-        <v>9680</v>
+        <v>15640</v>
       </c>
       <c r="Q17" t="n">
-        <v>371</v>
+        <v>5470</v>
       </c>
       <c r="R17" t="n">
-        <v>-10000</v>
+        <v>-84000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 및 구주 매각 이슈로 인한 악재 발생, 하한가 기록.</t>
+          <t>주가 상승에 대한 강한 기대감과 함께 2백만원 목표가 언급. 순환매 및 호재 가능성 제기. 공매도 세력에 대한 경계심 존재.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재', '하한가']</t>
+          <t>['순환매', '공매도', '호재']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2027,6 +2027,190 @@
         </is>
       </c>
       <c r="Z17" t="inlineStr">
+        <is>
+          <t>064550</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>아난티</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5435</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-4.82%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E18" t="n">
+        <v>51</v>
+      </c>
+      <c r="F18" t="n">
+        <v>40</v>
+      </c>
+      <c r="G18" t="n">
+        <v>150</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>5710</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5640</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5650</v>
+      </c>
+      <c r="M18" t="n">
+        <v>5270</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="O18" t="n">
+        <v>11756896085</v>
+      </c>
+      <c r="P18" t="n">
+        <v>10480</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3150</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-307000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>하락세에 대한 우려와 함께 외인·연기금의 매수세, 북한 관련 이슈 언급. 주가 조작 의혹 제기.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>['외인매수', '대북주', '주가조작']</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>025980</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>본느</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5240</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-8.71%</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>79</v>
+      </c>
+      <c r="F19" t="n">
+        <v>44</v>
+      </c>
+      <c r="G19" t="n">
+        <v>168</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>5740</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5250</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5420</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2368134080</v>
+      </c>
+      <c r="P19" t="n">
+        <v>9680</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>371</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>반기보고서 제출 지연 및 악재성 기사 출현으로 하한가 예상. 주가 하락에 대한 우려와 함께 일부 투자자들의 탈출 언급. 구주 매각 관련 불확실성 존재.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>['반기보고서', '악재 뉴스', '구주 매각']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>226340</t>
         </is>

--- a/data/trending_integrated_20260907_10.xlsx
+++ b/data/trending_integrated_20260907_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52300</v>
+        <v>51800</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+19.27%</t>
+          <t>+18.13%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.47</v>
       </c>
       <c r="E2" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F2" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G2" t="n">
-        <v>419</v>
+        <v>453</v>
       </c>
       <c r="H2" t="n">
         <v>14.18</v>
@@ -610,7 +610,7 @@
         <v>13.71</v>
       </c>
       <c r="O2" t="n">
-        <v>96427909375</v>
+        <v>101946804075</v>
       </c>
       <c r="P2" t="n">
         <v>108900</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>공매도 감소 및 우상향 추세 언급, 전고점 돌파 및 6-7만원 구간 매물대 약화 전망. 큰 폭 상승 마감.</t>
+          <t>공매도 감소 및 전고점 돌파 기대감. 6~7만원 구간 매물벽 약세 전망. 긍정적 우상향 추세.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['공매도', '우상향', '매물대']</t>
+          <t>['공매도', '전고점', '우상향']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.52</v>
       </c>
       <c r="E3" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G3" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H3" t="n">
         <v>1.25</v>
@@ -702,7 +702,7 @@
         <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>143932071492</v>
+        <v>146977492358</v>
       </c>
       <c r="P3" t="n">
         <v>3900</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>바이오니아, 삼익 등 타 종목 언급과 함께 긍정적 흐름 기대. '60% 상승' 등 구체적 전망 제시. 큰 폭 상승 마감.</t>
+          <t>금주 60% 이상 상승 전망. 월가 급등 및 거래량 증가 기대. 삼익, 제이신약과의 비교 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['바이오니아', '상승 전망']</t>
+          <t>['상승전망', '월가', '거래량']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>220000</v>
+        <v>6380</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+9.18%</t>
+          <t>+9.06%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.05</v>
+        <v>-0.7</v>
       </c>
       <c r="E4" t="n">
-        <v>282</v>
+        <v>66</v>
       </c>
       <c r="F4" t="n">
-        <v>163</v>
+        <v>41</v>
       </c>
       <c r="G4" t="n">
-        <v>799</v>
+        <v>250</v>
       </c>
       <c r="H4" t="n">
-        <v>29.46</v>
+        <v>1.61</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>201500</v>
+        <v>5850</v>
       </c>
       <c r="K4" t="n">
-        <v>212500</v>
+        <v>6000</v>
       </c>
       <c r="L4" t="n">
-        <v>225500</v>
+        <v>6525</v>
       </c>
       <c r="M4" t="n">
-        <v>212500</v>
+        <v>5940</v>
       </c>
       <c r="N4" t="n">
-        <v>29.51</v>
+        <v>2.31</v>
       </c>
       <c r="O4" t="n">
-        <v>235319289500</v>
+        <v>11773989395</v>
       </c>
       <c r="P4" t="n">
-        <v>438000</v>
+        <v>21500</v>
       </c>
       <c r="Q4" t="n">
-        <v>74700</v>
+        <v>2300</v>
       </c>
       <c r="R4" t="n">
-        <v>317000</v>
+        <v>-35000</v>
       </c>
       <c r="S4" t="n">
-        <v>102000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇 사업 및 액추에이터 기술 관련 호재와 프로그램 매수세 유입에 따른 기대감.</t>
+          <t>폐암학회 관련 기대감 및 신약 개발 가능성 언급. 저점 매수 기회 및 보유 권고. 다만, 6,500원 돌파 필요성 제기.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇사업', '액추에이터', '프로그램매수']</t>
+          <t>['폐암학회', '신약 개발', '저점 매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6370</v>
+        <v>218500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+8.89%</t>
+          <t>+8.44%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.7</v>
+        <v>-0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>59</v>
+        <v>290</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>166</v>
       </c>
       <c r="G5" t="n">
-        <v>227</v>
+        <v>841</v>
       </c>
       <c r="H5" t="n">
-        <v>1.61</v>
+        <v>29.46</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5850</v>
+        <v>201500</v>
       </c>
       <c r="K5" t="n">
-        <v>6000</v>
+        <v>212500</v>
       </c>
       <c r="L5" t="n">
-        <v>6490</v>
+        <v>225500</v>
       </c>
       <c r="M5" t="n">
-        <v>5940</v>
+        <v>212500</v>
       </c>
       <c r="N5" t="n">
-        <v>2.31</v>
+        <v>29.51</v>
       </c>
       <c r="O5" t="n">
-        <v>10650637125</v>
+        <v>240706070000</v>
       </c>
       <c r="P5" t="n">
-        <v>21500</v>
+        <v>438000</v>
       </c>
       <c r="Q5" t="n">
-        <v>2300</v>
+        <v>74700</v>
       </c>
       <c r="R5" t="n">
-        <v>-35000</v>
+        <v>317000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>102000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>세계폐암학회 관련 뉴스와 신약 개발 가능성에 대한 기대감이 높음. 보유 및 저점 추매 권유가 있으며, 공매도에 대한 언급도 존재. 주가 상승에 대한 강한 의지 표현.</t>
+          <t>로봇 사업 진출 및 기술력 부각. CES 2024 관련 긍정적 뉴스 및 프로그램 매수세 유입. 23만 탈환 및 100조 시총 저평가 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['신약 개발', '세계폐암학회', '공매도']</t>
+          <t>['로봇', 'CES 2024', '프로그램 매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>066570</t>
         </is>
       </c>
     </row>
@@ -946,13 +946,13 @@
         <v>-0.72</v>
       </c>
       <c r="E6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H6" t="n">
         <v>0.6</v>
@@ -978,7 +978,7 @@
         <v>1.32</v>
       </c>
       <c r="O6" t="n">
-        <v>78960682395</v>
+        <v>80371183605</v>
       </c>
       <c r="P6" t="n">
         <v>15960</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미프진 관련 언급 다수, 시장 기대감은 있으나 뚜렷한 근거 제시 부족. 등락률 소폭 상승.</t>
+          <t>미프진 공식화 및 단계적 도입 지시 관련 기대감. 외국인, 기관 순매수 진입.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['미프진', '기대감']</t>
+          <t>['미프진', '외국인', '기관']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25000</v>
+        <v>25400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+6.38%</t>
+          <t>+8.09%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="F7" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G7" t="n">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="H7" t="n">
         <v>0.16</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>321941425550</v>
+        <v>339471343850</v>
       </c>
       <c r="P7" t="n">
         <v>28750</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>CART 혈압계 관련 뉴스 언급, 서울대 등 유수 기관 협력 기반. 단기 급등 후 조정 및 향후 급등 가능성 언급. 소폭 상승 마감.</t>
+          <t>CART 혈압계 뉴스 및 서울대, 아산병원 등 임상 협력 기반 급등 기대. 세계 1위, 최초 타이틀.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['CART', '혈압계', '협력']</t>
+          <t>['CART', '혈압계', '임상']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1744000</v>
+        <v>1742000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.89%</t>
+          <t>+5.77%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="F8" t="n">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="G8" t="n">
-        <v>1914</v>
+        <v>1965</v>
       </c>
       <c r="H8" t="n">
         <v>50.5</v>
@@ -1162,7 +1162,7 @@
         <v>50.45</v>
       </c>
       <c r="O8" t="n">
-        <v>1784139813000</v>
+        <v>1962577041500</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>자사주 매입 및 외국인/기관 순매수세 유입에 따른 주가 상승 기대감 높음. 200만원 돌파 및 고공 행진 전망. 숏커버링 가능성 언급.</t>
+          <t>자사주 매입 및 외국인, 기관 순매수 지속. 200만원 돌파 및 숏커버링 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주매입', '외국인순매수', '숏커버링']</t>
+          <t>['자사주매입', '외국인', '숏커버링']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82900</v>
+        <v>83100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+4.67%</t>
+          <t>+4.92%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F9" t="n">
         <v>76</v>
       </c>
       <c r="G9" t="n">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="H9" t="n">
         <v>23.53</v>
@@ -1254,7 +1254,7 @@
         <v>23.61</v>
       </c>
       <c r="O9" t="n">
-        <v>119518966050</v>
+        <v>124297243000</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>하반기 본격 수주 및 대형 원전, 가스복합화력발전 언급. 기술력 입증 기반 상승 추세 전망. 큰 폭 상승 마감.</t>
+          <t>대미 투자 1호(가스복합) 계약 및 하반기 본격 수주 기대. 원자력주 전반적 상승세.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['하반기 수주', '대형 원전', '기술력']</t>
+          <t>['대미투자', '가스복합', '원자력']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13530</v>
+        <v>265000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.00%</t>
+          <t>+3.72%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.09</v>
+        <v>0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>51</v>
+        <v>795</v>
       </c>
       <c r="F10" t="n">
-        <v>38</v>
+        <v>467</v>
       </c>
       <c r="G10" t="n">
-        <v>214</v>
+        <v>2265</v>
       </c>
       <c r="H10" t="n">
-        <v>1.82</v>
+        <v>46.73</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13010</v>
+        <v>255500</v>
       </c>
       <c r="K10" t="n">
-        <v>13420</v>
+        <v>267000</v>
       </c>
       <c r="L10" t="n">
-        <v>14100</v>
+        <v>268000</v>
       </c>
       <c r="M10" t="n">
-        <v>13410</v>
+        <v>264000</v>
       </c>
       <c r="N10" t="n">
-        <v>1.91</v>
+        <v>46.71</v>
       </c>
       <c r="O10" t="n">
-        <v>54829891005</v>
+        <v>1304293699500</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>1252</v>
+        <v>69600</v>
       </c>
       <c r="R10" t="n">
-        <v>204000</v>
+        <v>1074000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>809000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>회사의 가치를 긍정적으로 평가하며, 당일 광통신주 대장으로서의 역할 기대. 공매도 물량 언급과 함께 주가 변동성에 대한 언급 존재.</t>
+          <t>애플 배당 및 샌디스크 폭등 뉴스 기반 반도체 섹터 상승 기대. 30만원 목표 매수세 유입.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신주', '공매도', '주가 변동성']</t>
+          <t>['반도체', '배당', '매수세']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>264750</v>
+        <v>13460</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+3.62%</t>
+          <t>+3.46%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>795</v>
+        <v>52</v>
       </c>
       <c r="F11" t="n">
-        <v>460</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
-        <v>2492</v>
+        <v>220</v>
       </c>
       <c r="H11" t="n">
-        <v>46.73</v>
+        <v>1.82</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>255500</v>
+        <v>13010</v>
       </c>
       <c r="K11" t="n">
-        <v>267000</v>
+        <v>13420</v>
       </c>
       <c r="L11" t="n">
-        <v>268000</v>
+        <v>14100</v>
       </c>
       <c r="M11" t="n">
-        <v>264000</v>
+        <v>13410</v>
       </c>
       <c r="N11" t="n">
-        <v>46.71</v>
+        <v>1.91</v>
       </c>
       <c r="O11" t="n">
-        <v>1203393250000</v>
+        <v>57156289370</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>69600</v>
+        <v>1252</v>
       </c>
       <c r="R11" t="n">
-        <v>1074000</v>
+        <v>204000</v>
       </c>
       <c r="S11" t="n">
-        <v>809000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>배당 및 목표 주가 언급, 반도체 관련 뉴스 인용. 긍정적 전망과 더불어 소폭 상승 마감.</t>
+          <t>회사의 가치를 긍정적으로 평가하며, 당일 광통신주 대장으로서의 역할 기대. 공매도 물량 언급과 함께 주가 변동성에 대한 언급 존재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['배당', '목표 주가', '반도체']</t>
+          <t>['광통신주', '공매도', '주가 변동성']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17400</v>
+        <v>17310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.26%</t>
+          <t>+2.73%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G12" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="H12" t="n">
         <v>10.4</v>
@@ -1530,7 +1530,7 @@
         <v>10.36</v>
       </c>
       <c r="O12" t="n">
-        <v>54569644560</v>
+        <v>57627212320</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>러우 전쟁 종전 분위기 및 중동 관련 언급, 주가 상승 기대감 표출. 소폭 상승 마감.</t>
+          <t>러우 전쟁 종전 분위기 및 중동 투자 관련 기대감. 외국인, 기관, 프매도 순매수.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['러우 전쟁', '중동']</t>
+          <t>['러우전쟁', '중동', '외국인']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,83 +1575,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6850</v>
+        <v>22925</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+2.09%</t>
+          <t>+1.89%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.85</v>
+        <v>0.62</v>
       </c>
       <c r="E13" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="H13" t="n">
-        <v>16.4</v>
+        <v>5.6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>6710</v>
+        <v>22500</v>
       </c>
       <c r="K13" t="n">
-        <v>6680</v>
+        <v>23100</v>
       </c>
       <c r="L13" t="n">
-        <v>7040</v>
+        <v>24000</v>
       </c>
       <c r="M13" t="n">
-        <v>6600</v>
+        <v>21500</v>
       </c>
       <c r="N13" t="n">
-        <v>15.55</v>
+        <v>4.98</v>
       </c>
       <c r="O13" t="n">
-        <v>7271284755</v>
+        <v>114111433750</v>
       </c>
       <c r="P13" t="n">
-        <v>13000</v>
+        <v>50600</v>
       </c>
       <c r="Q13" t="n">
-        <v>6030</v>
+        <v>9070</v>
       </c>
       <c r="R13" t="n">
-        <v>2000</v>
+        <v>-51000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>반도체 및 로봇 관련 언급, IPO 예정 기업 존재. 주가 부양 기대와 함께 '폭락주', '개미 털기' 등 부정적 언급 혼재. 소폭 상승 마감.</t>
+          <t>국민성장펀드 3500억 상장사. 거래량 주목, 신사업 진출 재료 부각. 다만, 투자 주의 종목 지정 및 급등락 반복.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체', '로봇', 'IPO']</t>
+          <t>['국민성장펀드', '신사업', '거래량']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22750</v>
+        <v>6830</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>+1.79%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="E14" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F14" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="G14" t="n">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="H14" t="n">
-        <v>5.6</v>
+        <v>16.4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>22500</v>
+        <v>6710</v>
       </c>
       <c r="K14" t="n">
-        <v>23100</v>
+        <v>6680</v>
       </c>
       <c r="L14" t="n">
-        <v>24000</v>
+        <v>7040</v>
       </c>
       <c r="M14" t="n">
-        <v>21500</v>
+        <v>6600</v>
       </c>
       <c r="N14" t="n">
-        <v>4.98</v>
+        <v>15.55</v>
       </c>
       <c r="O14" t="n">
-        <v>112588277225</v>
+        <v>7554808955</v>
       </c>
       <c r="P14" t="n">
-        <v>50600</v>
+        <v>13000</v>
       </c>
       <c r="Q14" t="n">
-        <v>9070</v>
+        <v>6030</v>
       </c>
       <c r="R14" t="n">
-        <v>-51000</v>
+        <v>2000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>국민성장펀드 관련 언급과 함께 거래량에 주목. 신사업 진출 및 로봇주 테마 상승 기대감 존재. 그러나 단기 급등락 및 투자주의 종목 지정 언급으로 변동성 우려.</t>
+          <t>한화로보틱스, 한화세미텍 IPO 예정. 반도체 및 로봇 사업 연계 분석. 흑자 회사 및 10000원 이상 목표가 제시. 외국인 순매수 확인.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['국민성장펀드', '로봇주', '거래량']</t>
+          <t>['IPO', '반도체', '로봇']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
@@ -1774,16 +1774,16 @@
         <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F15" t="n">
         <v>26</v>
       </c>
       <c r="G15" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H15" t="n">
-        <v>48.88</v>
+        <v>48.89</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>24.02</v>
       </c>
       <c r="O15" t="n">
-        <v>46245487700</v>
+        <v>47387889150</v>
       </c>
       <c r="P15" t="n">
         <v>31200</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>정배열 우상향 추세 및 공매도 물량 언급, 3만원 구간 지지선 기대. 소폭 상승 마감.</t>
+          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['정배열', '공매도', '지지선']</t>
+          <t>['환율', '반도체', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16080</v>
+        <v>15990</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F16" t="n">
         <v>43</v>
       </c>
       <c r="G16" t="n">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>24994319225</v>
+        <v>26292124990</v>
       </c>
       <c r="P16" t="n">
         <v>19380</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>메가 특구법 발의 및 호남 반도체 산단 관련 언급, 주가 상승 기대감 있으나 '개잡주' 등 부정적 표현 혼재. 소폭 하락 마감.</t>
+          <t>9월 메가특구법 발의 및 호남 반도체 산단 관련 기대감. '개잡주' 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['메가 특구법', '반도체 산단', '개잡주']</t>
+          <t>['메가특구법', '반도체', '호남']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10340</v>
+        <v>10260</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-1.25%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G17" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="H17" t="n">
         <v>5.75</v>
@@ -1990,7 +1990,7 @@
         <v>5.7</v>
       </c>
       <c r="O17" t="n">
-        <v>16925165495</v>
+        <v>17219936235</v>
       </c>
       <c r="P17" t="n">
         <v>15640</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 상승에 대한 강한 기대감과 함께 2백만원 목표가 언급. 순환매 및 호재 가능성 제기. 공매도 세력에 대한 경계심 존재.</t>
+          <t>급등 기대감 및 2백만원 목표가 제시. 공매도 소굴이라는 부정적 의견과 함께 매집 및 순환매 기대. 금일 12층 목표.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['순환매', '공매도', '호재']</t>
+          <t>['급등', '공매도', '순환매']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5435</v>
+        <v>5430</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.82%</t>
+          <t>-4.90%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.42</v>
       </c>
       <c r="E18" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18" t="n">
         <v>40</v>
       </c>
       <c r="G18" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H18" t="n">
         <v>4.81</v>
@@ -2082,7 +2082,7 @@
         <v>4.39</v>
       </c>
       <c r="O18" t="n">
-        <v>11756896085</v>
+        <v>12018243530</v>
       </c>
       <c r="P18" t="n">
         <v>10480</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>하락세에 대한 우려와 함께 외인·연기금의 매수세, 북한 관련 이슈 언급. 주가 조작 의혹 제기.</t>
+          <t>시진핑 방미 관련 뉴스 부재 및 하락 시작 우려. 대북주 변동성 및 주가 조작 의혹 제기. 외국인, 연기금 매수세 일부 확인.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['외인매수', '대북주', '주가조작']</t>
+          <t>['시진핑', '대북주', '주가 조작']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5240</v>
+        <v>5250</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-8.71%</t>
+          <t>-8.54%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F19" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G19" t="n">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2368134080</v>
+        <v>2400412680</v>
       </c>
       <c r="P19" t="n">
         <v>9680</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 및 악재성 기사 출현으로 하한가 예상. 주가 하락에 대한 우려와 함께 일부 투자자들의 탈출 언급. 구주 매각 관련 불확실성 존재.</t>
+          <t>반기 보고서 제출 지연 악재 및 조선비즈 기사로 인한 하한가 가능성 언급. 구미현 관련 논란 및 탈출 의견 다수.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재 뉴스', '구주 매각']</t>
+          <t>['반기 보고서', '악재', '구미현']</t>
         </is>
       </c>
       <c r="X19" t="n">

--- a/data/trending_integrated_20260907_10.xlsx
+++ b/data/trending_integrated_20260907_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51800</v>
+        <v>51900</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+18.13%</t>
+          <t>+18.36%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.47</v>
       </c>
       <c r="E2" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="F2" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G2" t="n">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="H2" t="n">
         <v>14.18</v>
@@ -610,7 +610,7 @@
         <v>13.71</v>
       </c>
       <c r="O2" t="n">
-        <v>101946804075</v>
+        <v>106285735675</v>
       </c>
       <c r="P2" t="n">
         <v>108900</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3655</v>
+        <v>3675</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+11.94%</t>
+          <t>+12.56%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.52</v>
       </c>
       <c r="E3" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G3" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="H3" t="n">
         <v>1.25</v>
@@ -702,7 +702,7 @@
         <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>146977492358</v>
+        <v>149696187048</v>
       </c>
       <c r="P3" t="n">
         <v>3900</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>금주 60% 이상 상승 전망. 월가 급등 및 거래량 증가 기대. 삼익, 제이신약과의 비교 언급.</t>
+          <t>월가 소식 및 특정 종목과의 동반 상승 기대감 있으나, 뚜렷한 근거는 부족.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['상승전망', '월가', '거래량']</t>
+          <t>['월가', '기대감']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6380</v>
+        <v>218000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+9.06%</t>
+          <t>+8.19%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.7</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>66</v>
+        <v>302</v>
       </c>
       <c r="F4" t="n">
-        <v>41</v>
+        <v>173</v>
       </c>
       <c r="G4" t="n">
-        <v>250</v>
+        <v>863</v>
       </c>
       <c r="H4" t="n">
-        <v>1.61</v>
+        <v>29.46</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>5850</v>
+        <v>201500</v>
       </c>
       <c r="K4" t="n">
-        <v>6000</v>
+        <v>212500</v>
       </c>
       <c r="L4" t="n">
-        <v>6525</v>
+        <v>225500</v>
       </c>
       <c r="M4" t="n">
-        <v>5940</v>
+        <v>212500</v>
       </c>
       <c r="N4" t="n">
-        <v>2.31</v>
+        <v>29.51</v>
       </c>
       <c r="O4" t="n">
-        <v>11773989395</v>
+        <v>246430637500</v>
       </c>
       <c r="P4" t="n">
-        <v>21500</v>
+        <v>438000</v>
       </c>
       <c r="Q4" t="n">
-        <v>2300</v>
+        <v>74700</v>
       </c>
       <c r="R4" t="n">
-        <v>-35000</v>
+        <v>317000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>102000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>폐암학회 관련 기대감 및 신약 개발 가능성 언급. 저점 매수 기회 및 보유 권고. 다만, 6,500원 돌파 필요성 제기.</t>
+          <t>로봇 사업 진출 및 기술력 부각. CES 2024 관련 긍정적 뉴스 및 프로그램 매수세 유입. 23만 탈환 및 100조 시총 저평가 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['폐암학회', '신약 개발', '저점 매수']</t>
+          <t>['로봇', 'CES 2024', '프로그램 매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>066570</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>218500</v>
+        <v>8600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+8.44%</t>
+          <t>+8.18%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.05</v>
+        <v>-0.72</v>
       </c>
       <c r="E5" t="n">
-        <v>290</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
-        <v>166</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>841</v>
+        <v>92</v>
       </c>
       <c r="H5" t="n">
-        <v>29.46</v>
+        <v>0.6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>201500</v>
+        <v>7950</v>
       </c>
       <c r="K5" t="n">
-        <v>212500</v>
+        <v>8200</v>
       </c>
       <c r="L5" t="n">
-        <v>225500</v>
+        <v>9210</v>
       </c>
       <c r="M5" t="n">
-        <v>212500</v>
+        <v>7980</v>
       </c>
       <c r="N5" t="n">
-        <v>29.51</v>
+        <v>1.32</v>
       </c>
       <c r="O5" t="n">
-        <v>240706070000</v>
+        <v>81295869340</v>
       </c>
       <c r="P5" t="n">
-        <v>438000</v>
+        <v>15960</v>
       </c>
       <c r="Q5" t="n">
-        <v>74700</v>
+        <v>3500</v>
       </c>
       <c r="R5" t="n">
-        <v>317000</v>
+        <v>208000</v>
       </c>
       <c r="S5" t="n">
-        <v>102000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>로봇 사업 진출 및 기술력 부각. CES 2024 관련 긍정적 뉴스 및 프로그램 매수세 유입. 23만 탈환 및 100조 시총 저평가 전망.</t>
+          <t>미프진 관련 소식과 함께 주가 상승 기대감이 있으나, 윗꼬리 달며 변동성이 큰 모습.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['로봇', 'CES 2024', '프로그램 매수']</t>
+          <t>['미프진', '변동성']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,77 +924,77 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8600</v>
+        <v>25350</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+8.18%</t>
+          <t>+7.87%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>51</v>
+        <v>341</v>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>163</v>
       </c>
       <c r="G6" t="n">
-        <v>82</v>
+        <v>461</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6</v>
+        <v>0.16</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7950</v>
+        <v>23500</v>
       </c>
       <c r="K6" t="n">
+        <v>23200</v>
+      </c>
+      <c r="L6" t="n">
+        <v>26450</v>
+      </c>
+      <c r="M6" t="n">
+        <v>22800</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>359190114375</v>
+      </c>
+      <c r="P6" t="n">
+        <v>28750</v>
+      </c>
+      <c r="Q6" t="n">
         <v>8200</v>
       </c>
-      <c r="L6" t="n">
-        <v>9210</v>
-      </c>
-      <c r="M6" t="n">
-        <v>7980</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="O6" t="n">
-        <v>80371183605</v>
-      </c>
-      <c r="P6" t="n">
-        <v>15960</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3500</v>
-      </c>
       <c r="R6" t="n">
-        <v>208000</v>
+        <v>-2000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>미프진 공식화 및 단계적 도입 지시 관련 기대감. 외국인, 기관 순매수 진입.</t>
+          <t>CART 혈압계 관련 뉴스 및 서울대/아산병원 등 주요 기관 임상 진입 사실.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['미프진', '외국인', '기관']</t>
+          <t>['CART', '임상', '뉴스']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,86 +1016,86 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25400</v>
+        <v>6310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+8.09%</t>
+          <t>+7.86%</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>66</v>
+      </c>
+      <c r="F7" t="n">
+        <v>41</v>
+      </c>
+      <c r="G7" t="n">
+        <v>266</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>5850</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6525</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5940</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="O7" t="n">
+        <v>11952651545</v>
+      </c>
+      <c r="P7" t="n">
+        <v>21500</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2300</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-35000</v>
+      </c>
+      <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="n">
-        <v>318</v>
-      </c>
-      <c r="F7" t="n">
-        <v>152</v>
-      </c>
-      <c r="G7" t="n">
-        <v>378</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>23500</v>
-      </c>
-      <c r="K7" t="n">
-        <v>23200</v>
-      </c>
-      <c r="L7" t="n">
-        <v>26450</v>
-      </c>
-      <c r="M7" t="n">
-        <v>22800</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>339471343850</v>
-      </c>
-      <c r="P7" t="n">
-        <v>28750</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>8200</v>
-      </c>
-      <c r="R7" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-1000</v>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>CART 혈압계 뉴스 및 서울대, 아산병원 등 임상 협력 기반 급등 기대. 세계 1위, 최초 타이틀.</t>
+          <t>현대바이오 홈페이지 공지 및 세계폐암학회 관련 내용 언급, 신약 개발 가능성 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['CART', '혈압계', '임상']</t>
+          <t>['현대바이오', '폐암학회', '신약']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1742000</v>
+        <v>84300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+5.77%</t>
+          <t>+6.44%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>795</v>
+        <v>113</v>
       </c>
       <c r="F8" t="n">
-        <v>446</v>
+        <v>76</v>
       </c>
       <c r="G8" t="n">
-        <v>1965</v>
+        <v>373</v>
       </c>
       <c r="H8" t="n">
-        <v>50.5</v>
+        <v>23.53</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1647000</v>
+        <v>79200</v>
       </c>
       <c r="K8" t="n">
-        <v>1737000</v>
+        <v>80200</v>
       </c>
       <c r="L8" t="n">
-        <v>1751000</v>
+        <v>84700</v>
       </c>
       <c r="M8" t="n">
-        <v>1733000</v>
+        <v>79000</v>
       </c>
       <c r="N8" t="n">
-        <v>50.45</v>
+        <v>23.61</v>
       </c>
       <c r="O8" t="n">
-        <v>1962577041500</v>
+        <v>143610861400</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>274000</v>
+        <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>281000</v>
+        <v>5000</v>
       </c>
       <c r="S8" t="n">
-        <v>146000</v>
+        <v>1000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>자사주 매입 및 외국인, 기관 순매수 지속. 200만원 돌파 및 숏커버링 기대감.</t>
+          <t>대미 투자 1호 가스복합 발전소 수주 기반 하반기 본격 수주 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주매입', '외국인', '숏커버링']</t>
+          <t>['대미투자', '가스복합', '원전']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83100</v>
+        <v>1737000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+4.92%</t>
+          <t>+5.46%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>113</v>
+        <v>796</v>
       </c>
       <c r="F9" t="n">
-        <v>76</v>
+        <v>447</v>
       </c>
       <c r="G9" t="n">
-        <v>355</v>
+        <v>2014</v>
       </c>
       <c r="H9" t="n">
-        <v>23.53</v>
+        <v>50.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>79200</v>
+        <v>1647000</v>
       </c>
       <c r="K9" t="n">
-        <v>80200</v>
+        <v>1737000</v>
       </c>
       <c r="L9" t="n">
-        <v>84400</v>
+        <v>1751000</v>
       </c>
       <c r="M9" t="n">
-        <v>79000</v>
+        <v>1733000</v>
       </c>
       <c r="N9" t="n">
-        <v>23.61</v>
+        <v>50.45</v>
       </c>
       <c r="O9" t="n">
-        <v>124297243000</v>
+        <v>2080964424500</v>
       </c>
       <c r="P9" t="n">
-        <v>139200</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>57000</v>
+        <v>274000</v>
       </c>
       <c r="R9" t="n">
-        <v>5000</v>
+        <v>281000</v>
       </c>
       <c r="S9" t="n">
-        <v>1000</v>
+        <v>146000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>대미 투자 1호(가스복합) 계약 및 하반기 본격 수주 기대. 원자력주 전반적 상승세.</t>
+          <t>자사주 매입 및 외국인/기관 순매수세 유입, 200만원 돌파 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['대미투자', '가스복합', '원자력']</t>
+          <t>['자사주매입', '외국인', '기관']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>265000</v>
+        <v>17640</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+3.72%</t>
+          <t>+4.69%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>795</v>
+        <v>47</v>
       </c>
       <c r="F10" t="n">
-        <v>467</v>
+        <v>31</v>
       </c>
       <c r="G10" t="n">
-        <v>2265</v>
+        <v>152</v>
       </c>
       <c r="H10" t="n">
-        <v>46.73</v>
+        <v>10.4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>255500</v>
+        <v>16850</v>
       </c>
       <c r="K10" t="n">
-        <v>267000</v>
+        <v>16870</v>
       </c>
       <c r="L10" t="n">
-        <v>268000</v>
+        <v>17770</v>
       </c>
       <c r="M10" t="n">
-        <v>264000</v>
+        <v>16590</v>
       </c>
       <c r="N10" t="n">
-        <v>46.71</v>
+        <v>10.36</v>
       </c>
       <c r="O10" t="n">
-        <v>1304293699500</v>
+        <v>60435920295</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>69600</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>1074000</v>
+        <v>82000</v>
       </c>
       <c r="S10" t="n">
-        <v>809000</v>
+        <v>-8000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>애플 배당 및 샌디스크 폭등 뉴스 기반 반도체 섹터 상승 기대. 30만원 목표 매수세 유입.</t>
+          <t>러우 전쟁 종전 분위기 및 중동 투자 기대감 속 원전 관련주 동반 상승.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['반도체', '배당', '매수세']</t>
+          <t>['원전', '러우전쟁', '중동']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13460</v>
+        <v>265500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+3.46%</t>
+          <t>+3.91%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.09</v>
+        <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>795</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>474</v>
       </c>
       <c r="G11" t="n">
-        <v>220</v>
+        <v>2103</v>
       </c>
       <c r="H11" t="n">
-        <v>1.82</v>
+        <v>46.73</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13010</v>
+        <v>255500</v>
       </c>
       <c r="K11" t="n">
-        <v>13420</v>
+        <v>267000</v>
       </c>
       <c r="L11" t="n">
-        <v>14100</v>
+        <v>268000</v>
       </c>
       <c r="M11" t="n">
-        <v>13410</v>
+        <v>264000</v>
       </c>
       <c r="N11" t="n">
-        <v>1.91</v>
+        <v>46.71</v>
       </c>
       <c r="O11" t="n">
-        <v>57156289370</v>
+        <v>1349112367000</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>1252</v>
+        <v>69600</v>
       </c>
       <c r="R11" t="n">
-        <v>204000</v>
+        <v>1074000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>809000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>회사의 가치를 긍정적으로 평가하며, 당일 광통신주 대장으로서의 역할 기대. 공매도 물량 언급과 함께 주가 변동성에 대한 언급 존재.</t>
+          <t>반도체 섹터 호재 및 외국인/기관 순매수세 유입 속 30만원 목표 매수 의견.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신주', '공매도', '주가 변동성']</t>
+          <t>['반도체', '외국인', '기관']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17310</v>
+        <v>13480</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+2.73%</t>
+          <t>+3.61%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="E12" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G12" t="n">
-        <v>142</v>
+        <v>237</v>
       </c>
       <c r="H12" t="n">
-        <v>10.4</v>
+        <v>1.82</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16850</v>
+        <v>13010</v>
       </c>
       <c r="K12" t="n">
-        <v>16870</v>
+        <v>13420</v>
       </c>
       <c r="L12" t="n">
-        <v>17770</v>
+        <v>14100</v>
       </c>
       <c r="M12" t="n">
-        <v>16590</v>
+        <v>13410</v>
       </c>
       <c r="N12" t="n">
-        <v>10.36</v>
+        <v>1.91</v>
       </c>
       <c r="O12" t="n">
-        <v>57627212320</v>
+        <v>58784963700</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>1252</v>
       </c>
       <c r="R12" t="n">
-        <v>82000</v>
+        <v>204000</v>
       </c>
       <c r="S12" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>러우 전쟁 종전 분위기 및 중동 투자 관련 기대감. 외국인, 기관, 프매도 순매수.</t>
+          <t>광통신주 대장 언급 및 기대감 있으나, 잦은 매도 공방과 요동치는 주가 흐름.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['러우전쟁', '중동', '외국인']</t>
+          <t>['광통신', '공매도', '변동성']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22925</v>
+        <v>6825</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+1.89%</t>
+          <t>+1.71%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="E13" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="G13" t="n">
-        <v>112</v>
+        <v>50</v>
       </c>
       <c r="H13" t="n">
-        <v>5.6</v>
+        <v>16.4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>22500</v>
+        <v>6710</v>
       </c>
       <c r="K13" t="n">
-        <v>23100</v>
+        <v>6680</v>
       </c>
       <c r="L13" t="n">
-        <v>24000</v>
+        <v>7040</v>
       </c>
       <c r="M13" t="n">
-        <v>21500</v>
+        <v>6600</v>
       </c>
       <c r="N13" t="n">
-        <v>4.98</v>
+        <v>15.55</v>
       </c>
       <c r="O13" t="n">
-        <v>114111433750</v>
+        <v>7901597015</v>
       </c>
       <c r="P13" t="n">
-        <v>50600</v>
+        <v>13000</v>
       </c>
       <c r="Q13" t="n">
-        <v>9070</v>
+        <v>6030</v>
       </c>
       <c r="R13" t="n">
-        <v>-51000</v>
+        <v>2000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>국민성장펀드 3500억 상장사. 거래량 주목, 신사업 진출 재료 부각. 다만, 투자 주의 종목 지정 및 급등락 반복.</t>
+          <t>한화세미텍, 한화로보틱스 IPO 예정. 반도체 및 로봇 사업 관련 기대감 존재. 현재 시점에서의 매수/매도 관련 혼조세.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['국민성장펀드', '신사업', '거래량']</t>
+          <t>['IPO', '로봇', '반도체']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6830</v>
+        <v>22700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+1.79%</t>
+          <t>+0.89%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.85</v>
+        <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F14" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G14" t="n">
-        <v>46</v>
+        <v>114</v>
       </c>
       <c r="H14" t="n">
-        <v>16.4</v>
+        <v>5.6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>6710</v>
+        <v>22500</v>
       </c>
       <c r="K14" t="n">
-        <v>6680</v>
+        <v>23100</v>
       </c>
       <c r="L14" t="n">
-        <v>7040</v>
+        <v>24000</v>
       </c>
       <c r="M14" t="n">
-        <v>6600</v>
+        <v>21500</v>
       </c>
       <c r="N14" t="n">
-        <v>15.55</v>
+        <v>4.98</v>
       </c>
       <c r="O14" t="n">
-        <v>7554808955</v>
+        <v>115922548050</v>
       </c>
       <c r="P14" t="n">
-        <v>13000</v>
+        <v>50600</v>
       </c>
       <c r="Q14" t="n">
-        <v>6030</v>
+        <v>9070</v>
       </c>
       <c r="R14" t="n">
-        <v>2000</v>
+        <v>-51000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>한화로보틱스, 한화세미텍 IPO 예정. 반도체 및 로봇 사업 연계 분석. 흑자 회사 및 10000원 이상 목표가 제시. 외국인 순매수 확인.</t>
+          <t>로봇주 상승세 속 신사업 진출 재료 언급되나, 투자주의 환기 종목 지정 및 하락 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['IPO', '반도체', '로봇']</t>
+          <t>['로봇주', '신사업', '투자주의']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
@@ -1763,27 +1763,27 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30250</v>
+        <v>30150</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H15" t="n">
-        <v>48.89</v>
+        <v>48.91</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         <v>24.02</v>
       </c>
       <c r="O15" t="n">
-        <v>47387889150</v>
+        <v>50417824400</v>
       </c>
       <c r="P15" t="n">
         <v>31200</v>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -1866,13 +1866,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F16" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G16" t="n">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>26292124990</v>
+        <v>27183157400</v>
       </c>
       <c r="P16" t="n">
         <v>19380</v>
@@ -1958,13 +1958,13 @@
         <v>0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F17" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G17" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H17" t="n">
         <v>5.75</v>
@@ -1990,7 +1990,7 @@
         <v>5.7</v>
       </c>
       <c r="O17" t="n">
-        <v>17219936235</v>
+        <v>17472216145</v>
       </c>
       <c r="P17" t="n">
         <v>15640</v>
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5430</v>
+        <v>5450</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.90%</t>
+          <t>-4.55%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2056,7 +2056,7 @@
         <v>40</v>
       </c>
       <c r="G18" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="H18" t="n">
         <v>4.81</v>
@@ -2082,7 +2082,7 @@
         <v>4.39</v>
       </c>
       <c r="O18" t="n">
-        <v>12018243530</v>
+        <v>12200277065</v>
       </c>
       <c r="P18" t="n">
         <v>10480</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5250</v>
+        <v>5270</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-8.54%</t>
+          <t>-8.19%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>83</v>
       </c>
       <c r="F19" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G19" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2400412680</v>
+        <v>2495393030</v>
       </c>
       <c r="P19" t="n">
         <v>9680</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>반기 보고서 제출 지연 악재 및 조선비즈 기사로 인한 하한가 가능성 언급. 구미현 관련 논란 및 탈출 의견 다수.</t>
+          <t>반기보고서 제출 지연 및 구주 매각 관련 악재 발생. 조선비즈 기사 언급 및 투심 훼손 우려. 일부 투자자들은 이미 탈출.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['반기 보고서', '악재', '구미현']</t>
+          <t>['반기보고서', '악재', '투심 훼손']</t>
         </is>
       </c>
       <c r="X19" t="n">

--- a/data/trending_integrated_20260907_10.xlsx
+++ b/data/trending_integrated_20260907_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51900</v>
+        <v>50900</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+18.36%</t>
+          <t>+16.08%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.47</v>
       </c>
       <c r="E2" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F2" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G2" t="n">
-        <v>471</v>
+        <v>499</v>
       </c>
       <c r="H2" t="n">
         <v>14.18</v>
@@ -610,7 +610,7 @@
         <v>13.71</v>
       </c>
       <c r="O2" t="n">
-        <v>106285735675</v>
+        <v>111097326825</v>
       </c>
       <c r="P2" t="n">
         <v>108900</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>공매도 감소 및 전고점 돌파 기대감. 6~7만원 구간 매물벽 약세 전망. 긍정적 우상향 추세.</t>
+          <t>수소 관련 성장 기대감 및 공매도 감소 추세. 전고점 돌파 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['공매도', '전고점', '우상향']</t>
+          <t>['수소', '공매도', '전고점']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3675</v>
+        <v>3640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+12.56%</t>
+          <t>+11.49%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.52</v>
       </c>
       <c r="E3" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F3" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="H3" t="n">
         <v>1.25</v>
@@ -702,7 +702,7 @@
         <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>149696187048</v>
+        <v>151890669427</v>
       </c>
       <c r="P3" t="n">
         <v>3900</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>월가 소식 및 특정 종목과의 동반 상승 기대감 있으나, 뚜렷한 근거는 부족.</t>
+          <t>뚜렷한 근거 없는 단기 급등 기대감. 거래량 대비 상승폭 제한.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['월가', '기대감']</t>
+          <t>['단기 급등', '거래량', '바이오']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>218000</v>
+        <v>26000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+8.19%</t>
+          <t>+10.64%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>302</v>
+        <v>371</v>
       </c>
       <c r="F4" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G4" t="n">
-        <v>863</v>
+        <v>514</v>
       </c>
       <c r="H4" t="n">
-        <v>29.46</v>
+        <v>0.16</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>201500</v>
+        <v>23500</v>
       </c>
       <c r="K4" t="n">
-        <v>212500</v>
+        <v>23200</v>
       </c>
       <c r="L4" t="n">
-        <v>225500</v>
+        <v>26700</v>
       </c>
       <c r="M4" t="n">
-        <v>212500</v>
+        <v>22800</v>
       </c>
       <c r="N4" t="n">
-        <v>29.51</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>246430637500</v>
+        <v>410518505575</v>
       </c>
       <c r="P4" t="n">
-        <v>438000</v>
+        <v>28750</v>
       </c>
       <c r="Q4" t="n">
-        <v>74700</v>
+        <v>8200</v>
       </c>
       <c r="R4" t="n">
-        <v>317000</v>
+        <v>-2000</v>
       </c>
       <c r="S4" t="n">
-        <v>102000</v>
+        <v>-1000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇 사업 진출 및 기술력 부각. CES 2024 관련 긍정적 뉴스 및 프로그램 매수세 유입. 23만 탈환 및 100조 시총 저평가 전망.</t>
+          <t>CART 혈압계 뉴스 및 기술력 부각. 세계 1위/최초 타이틀 강조. 3만원 돌파 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇', 'CES 2024', '프로그램 매수']</t>
+          <t>['CART 혈압계', '세계 1위', '최초']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8600</v>
+        <v>6380</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+8.18%</t>
+          <t>+9.06%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.72</v>
+        <v>-0.7</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>92</v>
+        <v>278</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6</v>
+        <v>1.61</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7950</v>
+        <v>5850</v>
       </c>
       <c r="K5" t="n">
-        <v>8200</v>
+        <v>6000</v>
       </c>
       <c r="L5" t="n">
-        <v>9210</v>
+        <v>6525</v>
       </c>
       <c r="M5" t="n">
-        <v>7980</v>
+        <v>5940</v>
       </c>
       <c r="N5" t="n">
-        <v>1.32</v>
+        <v>2.31</v>
       </c>
       <c r="O5" t="n">
-        <v>81295869340</v>
+        <v>12078412335</v>
       </c>
       <c r="P5" t="n">
-        <v>15960</v>
+        <v>21500</v>
       </c>
       <c r="Q5" t="n">
-        <v>3500</v>
+        <v>2300</v>
       </c>
       <c r="R5" t="n">
-        <v>208000</v>
+        <v>-35000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미프진 관련 소식과 함께 주가 상승 기대감이 있으나, 윗꼬리 달며 변동성이 큰 모습.</t>
+          <t>현대바이오 홈페이지 공지 및 폐암 관련 재료 언급. 19년 만에 서울 찾은 세계폐암학회 소식과 신약 개발 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['미프진', '변동성']</t>
+          <t>['폐암', '신약 개발', '홈페이지 공지']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25350</v>
+        <v>218500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+7.87%</t>
+          <t>+8.44%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>341</v>
+        <v>315</v>
       </c>
       <c r="F6" t="n">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="G6" t="n">
-        <v>461</v>
+        <v>898</v>
       </c>
       <c r="H6" t="n">
-        <v>0.16</v>
+        <v>29.46</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>23500</v>
+        <v>201500</v>
       </c>
       <c r="K6" t="n">
-        <v>23200</v>
+        <v>212500</v>
       </c>
       <c r="L6" t="n">
-        <v>26450</v>
+        <v>225500</v>
       </c>
       <c r="M6" t="n">
-        <v>22800</v>
+        <v>212500</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>29.51</v>
       </c>
       <c r="O6" t="n">
-        <v>359190114375</v>
+        <v>253789224000</v>
       </c>
       <c r="P6" t="n">
-        <v>28750</v>
+        <v>438000</v>
       </c>
       <c r="Q6" t="n">
-        <v>8200</v>
+        <v>74700</v>
       </c>
       <c r="R6" t="n">
-        <v>-2000</v>
+        <v>317000</v>
       </c>
       <c r="S6" t="n">
-        <v>-1000</v>
+        <v>102000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>CART 혈압계 관련 뉴스 및 서울대/아산병원 등 주요 기관 임상 진입 사실.</t>
+          <t>로봇 사업 진출 및 기술력 부각. CES 2024 관련 긍정적 뉴스 및 프로그램 매수세 유입. 23만 탈환 및 100조 시총 저평가 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['CART', '임상', '뉴스']</t>
+          <t>['로봇', 'CES 2024', '프로그램 매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>066570</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6310</v>
+        <v>8520</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+7.86%</t>
+          <t>+7.17%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.7</v>
+        <v>-0.72</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>266</v>
+        <v>96</v>
       </c>
       <c r="H7" t="n">
-        <v>1.61</v>
+        <v>0.6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>5850</v>
+        <v>7950</v>
       </c>
       <c r="K7" t="n">
-        <v>6000</v>
+        <v>8200</v>
       </c>
       <c r="L7" t="n">
-        <v>6525</v>
+        <v>9210</v>
       </c>
       <c r="M7" t="n">
-        <v>5940</v>
+        <v>7980</v>
       </c>
       <c r="N7" t="n">
-        <v>2.31</v>
+        <v>1.32</v>
       </c>
       <c r="O7" t="n">
-        <v>11952651545</v>
+        <v>82497687765</v>
       </c>
       <c r="P7" t="n">
-        <v>21500</v>
+        <v>15960</v>
       </c>
       <c r="Q7" t="n">
-        <v>2300</v>
+        <v>3500</v>
       </c>
       <c r="R7" t="n">
-        <v>-35000</v>
+        <v>208000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>현대바이오 홈페이지 공지 및 세계폐암학회 관련 내용 언급, 신약 개발 가능성 기대.</t>
+          <t>미프진 관련 기대감 및 거래량 증가 속 가격 변동성 확대. 긍정적 수급 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['현대바이오', '폐암학회', '신약']</t>
+          <t>['미프진', '거래량', '수급']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>84300</v>
+        <v>83750</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+6.44%</t>
+          <t>+5.74%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F8" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G8" t="n">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="H8" t="n">
         <v>23.53</v>
@@ -1162,7 +1162,7 @@
         <v>23.61</v>
       </c>
       <c r="O8" t="n">
-        <v>143610861400</v>
+        <v>147923841300</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1737000</v>
+        <v>1737500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+5.46%</t>
+          <t>+5.49%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F9" t="n">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="G9" t="n">
-        <v>2014</v>
+        <v>1890</v>
       </c>
       <c r="H9" t="n">
         <v>50.5</v>
@@ -1254,7 +1254,7 @@
         <v>50.45</v>
       </c>
       <c r="O9" t="n">
-        <v>2080964424500</v>
+        <v>2169070398500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>자사주 매입 및 외국인/기관 순매수세 유입, 200만원 돌파 기대감.</t>
+          <t>자사주 매입 기대감 및 외국인/기관 순매수세 유입. 200만원 터치 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['자사주매입', '외국인', '기관']</t>
+          <t>['자사주 매입', '외국인', '기관']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17640</v>
+        <v>17530</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+4.69%</t>
+          <t>+4.04%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="H10" t="n">
         <v>10.4</v>
@@ -1346,7 +1346,7 @@
         <v>10.36</v>
       </c>
       <c r="O10" t="n">
-        <v>60435920295</v>
+        <v>62227920420</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>러우 전쟁 종전 분위기 및 중동 투자 기대감 속 원전 관련주 동반 상승.</t>
+          <t>러우전쟁 종전 기대감 속 건설주 동반 상승. 5% 수익 실현.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['원전', '러우전쟁', '중동']</t>
+          <t>['러우전쟁', '건설주', '종전']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,83 +1391,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>265500</v>
+        <v>13530</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+3.91%</t>
+          <t>+4.00%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>795</v>
+        <v>57</v>
       </c>
       <c r="F11" t="n">
-        <v>474</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>2103</v>
+        <v>231</v>
       </c>
       <c r="H11" t="n">
-        <v>46.73</v>
+        <v>1.82</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>255500</v>
+        <v>13010</v>
       </c>
       <c r="K11" t="n">
-        <v>267000</v>
+        <v>13420</v>
       </c>
       <c r="L11" t="n">
-        <v>268000</v>
+        <v>14100</v>
       </c>
       <c r="M11" t="n">
-        <v>264000</v>
+        <v>13410</v>
       </c>
       <c r="N11" t="n">
-        <v>46.71</v>
+        <v>1.91</v>
       </c>
       <c r="O11" t="n">
-        <v>1349112367000</v>
+        <v>59512415170</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>69600</v>
+        <v>1252</v>
       </c>
       <c r="R11" t="n">
-        <v>1074000</v>
+        <v>204000</v>
       </c>
       <c r="S11" t="n">
-        <v>809000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>반도체 섹터 호재 및 외국인/기관 순매수세 유입 속 30만원 목표 매수 의견.</t>
+          <t>광통신 섹터 강세 및 공매도 물량 소화 기대. 14000원 물린 개미.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체', '외국인', '기관']</t>
+          <t>['광통신', '공매도', '섹터']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13480</v>
+        <v>265500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+3.61%</t>
+          <t>+3.91%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.09</v>
+        <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>54</v>
+        <v>795</v>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>475</v>
       </c>
       <c r="G12" t="n">
-        <v>237</v>
+        <v>2019</v>
       </c>
       <c r="H12" t="n">
-        <v>1.82</v>
+        <v>46.73</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13010</v>
+        <v>255500</v>
       </c>
       <c r="K12" t="n">
-        <v>13420</v>
+        <v>267000</v>
       </c>
       <c r="L12" t="n">
-        <v>14100</v>
+        <v>268000</v>
       </c>
       <c r="M12" t="n">
-        <v>13410</v>
+        <v>264000</v>
       </c>
       <c r="N12" t="n">
-        <v>1.91</v>
+        <v>46.71</v>
       </c>
       <c r="O12" t="n">
-        <v>58784963700</v>
+        <v>1377602355500</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>1252</v>
+        <v>69600</v>
       </c>
       <c r="R12" t="n">
-        <v>204000</v>
+        <v>1074000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>809000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>광통신주 대장 언급 및 기대감 있으나, 잦은 매도 공방과 요동치는 주가 흐름.</t>
+          <t>반도체 업황 개선 기대감 및 외국인/기관 순매수세 유입. 3만원 복귀 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '공매도', '변동성']</t>
+          <t>['반도체', '외국인', '기관']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6825</v>
+        <v>6890</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+1.71%</t>
+          <t>+2.68%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.85</v>
       </c>
       <c r="E13" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H13" t="n">
         <v>16.4</v>
@@ -1622,7 +1622,7 @@
         <v>15.55</v>
       </c>
       <c r="O13" t="n">
-        <v>7901597015</v>
+        <v>8198118050</v>
       </c>
       <c r="P13" t="n">
         <v>13000</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>한화세미텍, 한화로보틱스 IPO 예정. 반도체 및 로봇 사업 관련 기대감 존재. 현재 시점에서의 매수/매도 관련 혼조세.</t>
+          <t>한화 세미텍, 한화 로보틱스 IPO 언급 및 반도체, 로봇 사업 관련 기대감. 하지만 일부 매도 움직임 관찰.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['IPO', '로봇', '반도체']</t>
+          <t>['IPO', '반도체', '로봇']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22700</v>
+        <v>22900</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.89%</t>
+          <t>+1.78%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="H14" t="n">
         <v>5.6</v>
@@ -1714,7 +1714,7 @@
         <v>4.98</v>
       </c>
       <c r="O14" t="n">
-        <v>115922548050</v>
+        <v>116834542225</v>
       </c>
       <c r="P14" t="n">
         <v>50600</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>로봇주 상승세 속 신사업 진출 재료 언급되나, 투자주의 환기 종목 지정 및 하락 우려.</t>
+          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['로봇주', '신사업', '투자주의']</t>
+          <t>['로봇주', '신사업', '2연상']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30150</v>
+        <v>16050</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F15" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
+        <v>327</v>
       </c>
       <c r="H15" t="n">
-        <v>48.91</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,91 +1791,91 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>30200</v>
+        <v>16090</v>
       </c>
       <c r="K15" t="n">
-        <v>30350</v>
+        <v>16150</v>
       </c>
       <c r="L15" t="n">
-        <v>30900</v>
+        <v>16480</v>
       </c>
       <c r="M15" t="n">
-        <v>29900</v>
+        <v>15830</v>
       </c>
       <c r="N15" t="n">
-        <v>24.02</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>50417824400</v>
+        <v>27834129940</v>
       </c>
       <c r="P15" t="n">
-        <v>31200</v>
+        <v>19380</v>
       </c>
       <c r="Q15" t="n">
-        <v>21000</v>
+        <v>3200</v>
       </c>
       <c r="R15" t="n">
-        <v>139000</v>
+        <v>-3000</v>
       </c>
       <c r="S15" t="n">
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
+          <t>메가특구법 발의 및 반도체 산단 조성 기대감. 15만원 목표.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['환율', '반도체', '공매도']</t>
+          <t>['메가특구법', '반도체', '산단']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15990</v>
+        <v>30100</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E16" t="n">
+        <v>36</v>
+      </c>
+      <c r="F16" t="n">
+        <v>23</v>
+      </c>
+      <c r="G16" t="n">
         <v>66</v>
       </c>
-      <c r="F16" t="n">
-        <v>45</v>
-      </c>
-      <c r="G16" t="n">
-        <v>303</v>
-      </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>48.92</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,60 +1883,60 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>16090</v>
+        <v>30200</v>
       </c>
       <c r="K16" t="n">
-        <v>16150</v>
+        <v>30350</v>
       </c>
       <c r="L16" t="n">
-        <v>16480</v>
+        <v>30900</v>
       </c>
       <c r="M16" t="n">
-        <v>15830</v>
+        <v>29900</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>24.02</v>
       </c>
       <c r="O16" t="n">
-        <v>27183157400</v>
+        <v>52251958925</v>
       </c>
       <c r="P16" t="n">
-        <v>19380</v>
+        <v>31200</v>
       </c>
       <c r="Q16" t="n">
-        <v>3200</v>
+        <v>21000</v>
       </c>
       <c r="R16" t="n">
-        <v>-3000</v>
+        <v>139000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>9월 메가특구법 발의 및 호남 반도체 산단 관련 기대감. '개잡주' 언급.</t>
+          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['메가특구법', '반도체', '호남']</t>
+          <t>['환율', '반도체', '공매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10260</v>
+        <v>10160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.25%</t>
+          <t>-2.21%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G17" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H17" t="n">
         <v>5.75</v>
@@ -1990,7 +1990,7 @@
         <v>5.7</v>
       </c>
       <c r="O17" t="n">
-        <v>17472216145</v>
+        <v>17666234955</v>
       </c>
       <c r="P17" t="n">
         <v>15640</v>
@@ -2050,7 +2050,7 @@
         <v>0.42</v>
       </c>
       <c r="E18" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" t="n">
         <v>40</v>
@@ -2082,7 +2082,7 @@
         <v>4.39</v>
       </c>
       <c r="O18" t="n">
-        <v>12200277065</v>
+        <v>12271334140</v>
       </c>
       <c r="P18" t="n">
         <v>10480</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5270</v>
+        <v>5300</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-8.19%</t>
+          <t>-7.67%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F19" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G19" t="n">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2495393030</v>
+        <v>2584933620</v>
       </c>
       <c r="P19" t="n">
         <v>9680</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 및 구주 매각 관련 악재 발생. 조선비즈 기사 언급 및 투심 훼손 우려. 일부 투자자들은 이미 탈출.</t>
+          <t>반기보고서 제출 지연 및 악재 뉴스로 인한 투심 훼손 우려. 구주 매각 불확실성과 기사 출현으로 인한 하한가 가능성 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재', '투심 훼손']</t>
+          <t>['반기보고서', '악재 뉴스', '투심 훼손']</t>
         </is>
       </c>
       <c r="X19" t="n">
